--- a/12625004.xlsx
+++ b/12625004.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MCA\PYTHON THEORY CLASS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Documents/GitHub/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBD7A826-A60D-4057-BD0B-09D346224F2F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1099,7 +1099,9 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
+      <c r="A9" s="13">
+        <v>46254</v>
+      </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>

--- a/12625004.xlsx
+++ b/12625004.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Documents/GitHub/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBD7A826-A60D-4057-BD0B-09D346224F2F}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CB48B2D-383E-460E-8D18-AB283392070A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -213,6 +213,24 @@
   <si>
     <t>felt bad because I cant did good today</t>
   </si>
+  <si>
+    <t>happy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">felt happy because during class I was understood all lecture </t>
+  </si>
+  <si>
+    <t>verage</t>
+  </si>
+  <si>
+    <t>avrage</t>
+  </si>
+  <si>
+    <t>felt aa liitle bit unhappy</t>
+  </si>
+  <si>
+    <t>I am feeling relaxed</t>
+  </si>
 </sst>
 </file>
 
@@ -221,7 +239,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +320,13 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -350,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -394,11 +419,38 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -490,6 +542,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1098,117 +1154,231 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="13">
         <v>46254</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="B9" s="14">
+        <v>480</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>420</v>
+      </c>
+      <c r="G9" s="14">
+        <v>7</v>
+      </c>
+      <c r="H9" s="14">
+        <v>120</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+        <v>210</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="14">
+        <v>540</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>180</v>
+      </c>
+      <c r="E10" s="14">
+        <v>60</v>
+      </c>
+      <c r="F10" s="14">
+        <v>360</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>120</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J10" s="15">
+        <v>210</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B11" s="14">
+        <v>600</v>
+      </c>
+      <c r="C11" s="14">
+        <v>30</v>
+      </c>
+      <c r="D11" s="14">
+        <v>240</v>
+      </c>
+      <c r="E11" s="14">
+        <v>120</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>120</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+        <v>330</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B12" s="14">
+        <v>600</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>240</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>120</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+        <v>390</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" s="21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B13" s="14">
+        <v>540</v>
+      </c>
+      <c r="C13" s="14">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14">
+        <v>240</v>
+      </c>
+      <c r="E13" s="14">
+        <v>120</v>
+      </c>
+      <c r="F13" s="14">
+        <v>120</v>
+      </c>
+      <c r="G13" s="14">
+        <v>2</v>
+      </c>
+      <c r="H13" s="14">
+        <v>120</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>1170</v>
+      </c>
+      <c r="J13" s="15"/>
+      <c r="K13" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
@@ -9919,21 +10089,26 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J19 J21:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6:J8 J21:J401 J14:J19">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J9:J13">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K19 K21:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K21:K401 K6:K19" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L19 L21:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L21:L401 L6:L19" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M19 M21:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M21:M401 M6:M19" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625004.xlsx
+++ b/12625004.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Documents/GitHub/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Desktop/776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CB48B2D-383E-460E-8D18-AB283392070A}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EA4342B-FFEE-4798-8B09-02956AA72E77}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -231,6 +231,9 @@
   <si>
     <t>I am feeling relaxed</t>
   </si>
+  <si>
+    <t>felt bit nervous</t>
+  </si>
 </sst>
 </file>
 
@@ -416,29 +419,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -542,10 +533,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -933,74 +920,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12625004</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1333,7 +1320,7 @@
       <c r="M12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="N12" s="18" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1381,26 +1368,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="14">
+        <v>540</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>350</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>120</v>
+      </c>
+      <c r="G14" s="14">
+        <v>2</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>220</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
@@ -10089,13 +10100,13 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J8 J21:J401 J14:J19">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="J6:J19">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J9:J13">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J21:J401">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12625004.xlsx
+++ b/12625004.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Desktop/776/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Documents/GitHub/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EA4342B-FFEE-4798-8B09-02956AA72E77}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8AA60F-CC41-4443-9024-281349DFFE5D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,7 +232,13 @@
     <t>I am feeling relaxed</t>
   </si>
   <si>
-    <t>felt bit nervous</t>
+    <t>2026-08025</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>I felt good</t>
   </si>
 </sst>
 </file>
@@ -535,6 +541,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1368,49 +1378,49 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13">
-        <v>46259</v>
+      <c r="A14" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="B14" s="14">
-        <v>540</v>
+        <v>350</v>
       </c>
       <c r="C14" s="14">
         <v>30</v>
       </c>
       <c r="D14" s="14">
+        <v>240</v>
+      </c>
+      <c r="E14" s="14">
+        <v>120</v>
+      </c>
+      <c r="F14" s="14">
         <v>350</v>
       </c>
-      <c r="E14" s="14">
-        <v>60</v>
-      </c>
-      <c r="F14" s="14">
-        <v>120</v>
-      </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H14" s="14">
         <v>120</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>55</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">

--- a/12625004.xlsx
+++ b/12625004.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Documents/GitHub/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0eb0b81235d0062c/Desktop/776/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA8AA60F-CC41-4443-9024-281349DFFE5D}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{E03027F0-8265-43BF-A0A2-E202A7C3F2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28FDDE51-F349-495D-9ADA-2267F3FFC65C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,13 +232,40 @@
     <t>I am feeling relaxed</t>
   </si>
   <si>
-    <t>2026-08025</t>
+    <t>felt bit nervous</t>
+  </si>
+  <si>
+    <t>felt sad</t>
+  </si>
+  <si>
+    <t>felt little happy</t>
+  </si>
+  <si>
+    <t>today went well so I feel relived</t>
+  </si>
+  <si>
+    <t>felt stressed</t>
+  </si>
+  <si>
+    <t>felt relaxed</t>
+  </si>
+  <si>
+    <t>felt happy</t>
+  </si>
+  <si>
+    <t>2026--08-31</t>
+  </si>
+  <si>
+    <t>averge</t>
+  </si>
+  <si>
+    <t>I felt very nervous because today was my CA and I can not perform well</t>
   </si>
   <si>
     <t>high</t>
   </si>
   <si>
-    <t>I felt good</t>
+    <t>I feltl good because today was my ca gone well</t>
   </si>
 </sst>
 </file>
@@ -384,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -428,6 +455,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -930,74 +958,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="22">
         <v>12625004</v>
       </c>
-      <c r="G2" s="21"/>
+      <c r="G2" s="22"/>
+      <c r="I2" s="19"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
     </row>
     <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1378,160 +1407,280 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13" t="s">
-        <v>65</v>
+      <c r="A14" s="13">
+        <v>46259</v>
       </c>
       <c r="B14" s="14">
-        <v>350</v>
+        <v>540</v>
       </c>
       <c r="C14" s="14">
         <v>30</v>
       </c>
       <c r="D14" s="14">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
         <v>120</v>
       </c>
-      <c r="F14" s="14">
-        <v>350</v>
-      </c>
       <c r="G14" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H14" s="14">
         <v>120</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1210</v>
+        <v>1220</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>55</v>
       </c>
       <c r="M14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="14">
+        <v>540</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>240</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>120</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="0"/>
+        <v>1340</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B16" s="14">
+        <v>540</v>
+      </c>
+      <c r="C16" s="14">
+        <v>30</v>
+      </c>
+      <c r="D16" s="14">
+        <v>240</v>
+      </c>
+      <c r="E16" s="14">
+        <v>120</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J16" s="15">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="N14" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    </row>
+    <row r="17" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="14">
+        <v>480</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>180</v>
+      </c>
+      <c r="E17" s="14">
+        <v>70</v>
+      </c>
+      <c r="F17" s="14">
+        <v>110</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>120</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+        <v>420</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A18" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="14">
+        <v>480</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>180</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>20</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:184" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
+      <c r="D19" s="14">
+        <v>180</v>
+      </c>
+      <c r="E19" s="14">
+        <v>60</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="20" spans="1:184" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
@@ -1542,8 +1691,14 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
+      <c r="I20" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J20" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
       <c r="K20" s="13"/>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
@@ -1720,92 +1875,188 @@
       <c r="GB20" s="13"/>
     </row>
     <row r="21" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="14">
+        <v>480</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>180</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>100</v>
+      </c>
+      <c r="G21" s="14">
+        <v>2</v>
+      </c>
+      <c r="H21" s="14">
+        <v>60</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="22" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B22" s="14">
+        <v>480</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>240</v>
+      </c>
+      <c r="E22" s="14">
+        <v>120</v>
+      </c>
+      <c r="F22" s="14">
+        <v>350</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>120</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+        <v>70</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:184" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B23" s="14">
+        <v>480</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>180</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
+        <v>200</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:184" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:184" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B24" s="14">
+        <v>480</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>180</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>350</v>
+      </c>
+      <c r="G24" s="14">
+        <v>7</v>
+      </c>
+      <c r="H24" s="14">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>190</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="25" spans="1:184" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>
@@ -10135,6 +10386,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>